--- a/data/trans_bre/KIDM_A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_A_R-Clase-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 0,0</t>
+          <t>-14,55; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,54</t>
+          <t>0,0; 12,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 0,0</t>
+          <t>-11,72; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 9,16</t>
+          <t>-5,69; 9,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,23</t>
+          <t>0,0; 10,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,9</t>
+          <t>0,0; 7,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,65</t>
+          <t>0,0; 15,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 10,9</t>
+          <t>-5,4; 11,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 3,39</t>
+          <t>-7,47; 3,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 7,11</t>
+          <t>-3,97; 7,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 0,0</t>
+          <t>-17,54; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,68</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 4,86</t>
+          <t>-6,13; 4,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 2,7</t>
+          <t>-6,94; 2,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,45</t>
+          <t>0,0; 7,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,43; 206,38</t>
+          <t>-78,39; 191,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-88,13; 230,55</t>
+          <t>-100,0; 320,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 7,31</t>
+          <t>-3,9; 6,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 2,76</t>
+          <t>-7,64; 2,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,1</t>
+          <t>0,0; 7,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,4</t>
+          <t>0,0; 9,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 17,1</t>
+          <t>-6,96; 18,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,6; -2,11</t>
+          <t>-17,67; -2,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,11</t>
+          <t>-1,97; 2,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,56</t>
+          <t>-2,68; 2,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,47</t>
+          <t>-1,97; 1,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,72</t>
+          <t>-1,89; 1,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-66,97; 226,52</t>
+          <t>-69,24; 215,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-57,61; 114,06</t>
+          <t>-57,66; 115,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-72,93; 163,31</t>
+          <t>-77,91; 183,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-95,75; 368,3</t>
+          <t>-88,1; 332,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/KIDM_A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_A_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 0,0</t>
+          <t>-14,71; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,72</t>
+          <t>0,0; 13,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 0,0</t>
+          <t>-13,07; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 9,06</t>
+          <t>-5,71; 9,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,38</t>
+          <t>0,0; 10,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,37</t>
+          <t>0,0; 6,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,28</t>
+          <t>0,0; 16,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 11,52</t>
+          <t>-5,4; 12,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 3,4</t>
+          <t>-9,08; 3,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 7,04</t>
+          <t>-4,09; 6,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 0,0</t>
+          <t>-16,91; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,63</t>
+          <t>0,0; 5,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 4,8</t>
+          <t>-6,38; 5,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 2,56</t>
+          <t>-6,55; 2,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,41</t>
+          <t>0,0; 6,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,39; 191,01</t>
+          <t>-78,28; 220,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 320,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 6,12</t>
+          <t>-3,16; 6,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 2,07</t>
+          <t>-7,72; 2,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,48</t>
+          <t>0,0; 6,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,0; 5,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,54</t>
+          <t>0,0; 9,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 18,25</t>
+          <t>-6,69; 18,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,67; -2,34</t>
+          <t>-18,5; -2,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 2,01</t>
+          <t>-1,74; 2,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,48</t>
+          <t>-2,84; 2,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,51</t>
+          <t>-1,88; 1,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,72</t>
+          <t>-2,01; 1,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-69,24; 215,45</t>
+          <t>-66,0; 204,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-57,66; 115,33</t>
+          <t>-58,89; 106,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-77,91; 183,31</t>
+          <t>-73,67; 202,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-88,1; 332,79</t>
+          <t>-100,0; 346,31</t>
         </is>
       </c>
     </row>
